--- a/SGC-CKN/Excel/ba953f63-6a33-4844-9d19-9a7904295c33_Lô_CT-02_P7-35_D800_26-05-2026.xlsx
+++ b/SGC-CKN/Excel/ba953f63-6a33-4844-9d19-9a7904295c33_Lô_CT-02_P7-35_D800_26-05-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>21:30 25/05/2026</t>
+    <t>21:30 25/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>06:10 26/05/2026</t>
+    <t>06:10 26/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">21:30
-25/05/2026</t>
+25/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:16
-25/05/2026</t>
+25/03/2026</t>
   </si>
   <si>
     <t/>
@@ -116,11 +116,11 @@
   </si>
   <si>
     <t xml:space="preserve">22:17
-25/05/2026</t>
+25/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:25
-25/05/2026</t>
+25/03/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -130,11 +130,11 @@
   </si>
   <si>
     <t xml:space="preserve">22:26
-25/05/2026</t>
+25/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">00:05
-26/05/2026</t>
+25/03/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -144,11 +144,11 @@
   </si>
   <si>
     <t xml:space="preserve">00:06
-26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:55
-26/05/2026</t>
+25/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:55
+25/03/2026</t>
   </si>
   <si>
     <t>14</t>
@@ -157,12 +157,12 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">02:18
-26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:42
-26/05/2026</t>
+    <t xml:space="preserve">00:56
+25/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:42
+25/03/2026</t>
   </si>
   <si>
     <t>15</t>
@@ -171,12 +171,12 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">04:48
-26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:36
-26/05/2026</t>
+    <t xml:space="preserve">01:43
+25/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03:36
+25/03/2026</t>
   </si>
   <si>
     <t>16</t>
@@ -185,12 +185,12 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">05:37
-26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:40
-26/05/2026</t>
+    <t xml:space="preserve">03:37
+25/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:00
+25/03/2026</t>
   </si>
   <si>
     <t>16.1</t>
@@ -199,29 +199,19 @@
     <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">05:41
-26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05:55
-26/05/2026</t>
-  </si>
-  <si>
-    <t>Cắt chân. Giờ viết tay 4h01-4h40 được điều chỉnh thành 5h41-5h55 theo logic tăng dần.</t>
+    <t xml:space="preserve">04:40
+25/03/2026</t>
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">05:56
-26/05/2026</t>
+    <t xml:space="preserve">04:45
+25/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">05:58
-26/05/2026</t>
-  </si>
-  <si>
-    <t>Giờ viết tay 4h46-5h58 được điều chỉnh thành 5h56-5h58 theo logic tăng dần.</t>
+25/03/2026</t>
   </si>
   <si>
     <t>17</t>
@@ -231,11 +221,11 @@
   </si>
   <si>
     <t xml:space="preserve">05:59
-26/05/2026</t>
+25/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">06:10
-26/05/2026</t>
+25/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1242,7 +1232,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.285</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.36</v>
@@ -1254,7 +1244,7 @@
         <v>7.36</v>
       </c>
       <c r="J11" s="8">
-        <v>5.32</v>
+        <v>9.6</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1280,16 +1270,16 @@
         <v>-7.36</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.57</v>
+        <v>-9.51</v>
       </c>
       <c r="H12" s="9">
         <v>0.13</v>
       </c>
       <c r="I12" s="9">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="J12" s="8">
-        <v>16.57</v>
+        <v>16.12</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1312,19 +1302,19 @@
         <v>38</v>
       </c>
       <c r="F13" s="12">
-        <v>-9.57</v>
+        <v>-9.51</v>
       </c>
       <c r="G13" s="12">
-        <v>-12.7</v>
+        <v>-17.7</v>
       </c>
       <c r="H13" s="12">
         <v>1.65</v>
       </c>
       <c r="I13" s="12">
-        <v>3.13</v>
+        <v>8.19</v>
       </c>
       <c r="J13" s="15">
-        <v>1.9</v>
+        <v>4.96</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1347,19 +1337,19 @@
         <v>42</v>
       </c>
       <c r="F14" s="16">
-        <v>-12.7</v>
+        <v>-17.7</v>
       </c>
       <c r="G14" s="16">
         <v>-21.89</v>
       </c>
       <c r="H14" s="16">
-        <v>1.82</v>
+        <v>0.82</v>
       </c>
       <c r="I14" s="16">
-        <v>9.19</v>
+        <v>4.19</v>
       </c>
       <c r="J14" s="8">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1388,13 +1378,13 @@
         <v>-25.89</v>
       </c>
       <c r="H15" s="19">
-        <v>2.4</v>
+        <v>0.77</v>
       </c>
       <c r="I15" s="19">
         <v>4</v>
       </c>
-      <c r="J15" s="15">
-        <v>1.67</v>
+      <c r="J15" s="8">
+        <v>5.22</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1423,13 +1413,13 @@
         <v>-35.7</v>
       </c>
       <c r="H16" s="22">
-        <v>0.8</v>
+        <v>1.88</v>
       </c>
       <c r="I16" s="22">
         <v>9.81</v>
       </c>
       <c r="J16" s="8">
-        <v>12.26</v>
+        <v>5.21</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1458,13 +1448,13 @@
         <v>-37.7</v>
       </c>
       <c r="H17" s="25">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
       <c r="I17" s="25">
         <v>2</v>
       </c>
       <c r="J17" s="8">
-        <v>40</v>
+        <v>5.22</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1481,10 +1471,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>57</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>58</v>
       </c>
       <c r="F18" s="28">
         <v>-37.7</v>
@@ -1493,16 +1483,16 @@
         <v>-39.2</v>
       </c>
       <c r="H18" s="28">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="I18" s="28">
         <v>1.5</v>
       </c>
-      <c r="J18" s="8">
-        <v>6.43</v>
+      <c r="J18" s="15">
+        <v>2.25</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1513,13 +1503,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>60</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>62</v>
       </c>
       <c r="F19" s="31">
         <v>-39.2</v>
@@ -1528,33 +1518,33 @@
         <v>-43.57</v>
       </c>
       <c r="H19" s="31">
-        <v>0.03</v>
+        <v>1.22</v>
       </c>
       <c r="I19" s="31">
         <v>4.37</v>
       </c>
-      <c r="J19" s="8">
-        <v>131.1</v>
+      <c r="J19" s="15">
+        <v>3.59</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F20" s="34">
         <v>-43.57</v>
@@ -1577,7 +1567,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1683,31 +1673,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1724,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.29</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.36</v>
@@ -1756,16 +1746,16 @@
         <v>-7.36</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.57</v>
+        <v>-9.51</v>
       </c>
       <c r="G3" s="9">
         <v>0.13</v>
       </c>
       <c r="H3" s="9">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="I3" s="8">
-        <v>16.57</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1782,19 +1772,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-9.57</v>
+        <v>-9.51</v>
       </c>
       <c r="F4" s="12">
-        <v>-12.7</v>
+        <v>-17.7</v>
       </c>
       <c r="G4" s="12">
         <v>1.65</v>
       </c>
       <c r="H4" s="12">
-        <v>3.13</v>
+        <v>8.19</v>
       </c>
       <c r="I4" s="15">
-        <v>1.9</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1811,19 +1801,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-12.7</v>
+        <v>-17.7</v>
       </c>
       <c r="F5" s="16">
         <v>-21.89</v>
       </c>
       <c r="G5" s="16">
-        <v>1.82</v>
+        <v>0.82</v>
       </c>
       <c r="H5" s="16">
-        <v>9.19</v>
+        <v>4.19</v>
       </c>
       <c r="I5" s="8">
-        <v>5.06</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1846,13 +1836,13 @@
         <v>-25.89</v>
       </c>
       <c r="G6" s="19">
-        <v>2.4</v>
+        <v>0.77</v>
       </c>
       <c r="H6" s="19">
         <v>4</v>
       </c>
-      <c r="I6" s="15">
-        <v>1.67</v>
+      <c r="I6" s="8">
+        <v>5.22</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1875,13 +1865,13 @@
         <v>-35.7</v>
       </c>
       <c r="G7" s="22">
-        <v>0.8</v>
+        <v>1.88</v>
       </c>
       <c r="H7" s="22">
         <v>9.81</v>
       </c>
       <c r="I7" s="8">
-        <v>12.26</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1904,13 +1894,13 @@
         <v>-37.7</v>
       </c>
       <c r="G8" s="25">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
       <c r="H8" s="25">
         <v>2</v>
       </c>
       <c r="I8" s="8">
-        <v>40</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1933,13 +1923,13 @@
         <v>-39.2</v>
       </c>
       <c r="G9" s="28">
-        <v>0.23</v>
+        <v>0.67</v>
       </c>
       <c r="H9" s="28">
         <v>1.5</v>
       </c>
-      <c r="I9" s="8">
-        <v>6.43</v>
+      <c r="I9" s="15">
+        <v>2.25</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1950,7 +1940,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1962,13 +1952,13 @@
         <v>-43.57</v>
       </c>
       <c r="G10" s="31">
-        <v>0.03</v>
+        <v>1.22</v>
       </c>
       <c r="H10" s="31">
         <v>4.37</v>
       </c>
-      <c r="I10" s="8">
-        <v>131.1</v>
+      <c r="I10" s="15">
+        <v>3.59</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1979,7 +1969,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -2002,7 +1992,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -2014,19 +2004,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.29</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-44.65</v>
       </c>
       <c r="G12" s="39">
-        <v>8.07</v>
+        <v>8.47</v>
       </c>
       <c r="H12" s="39">
         <v>44.65</v>
       </c>
       <c r="I12" s="39">
-        <v>5.54</v>
+        <v>5.27</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/ba953f63-6a33-4844-9d19-9a7904295c33_Lô_CT-02_P7-35_D800_26-05-2026.xlsx
+++ b/SGC-CKN/Excel/ba953f63-6a33-4844-9d19-9a7904295c33_Lô_CT-02_P7-35_D800_26-05-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
   <si>
     <t>Dự án</t>
   </si>
@@ -134,7 +134,7 @@
   </si>
   <si>
     <t xml:space="preserve">00:05
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -144,11 +144,11 @@
   </si>
   <si>
     <t xml:space="preserve">00:06
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">00:55
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t>14</t>
@@ -158,11 +158,11 @@
   </si>
   <si>
     <t xml:space="preserve">00:56
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">01:42
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t>15</t>
@@ -172,11 +172,11 @@
   </si>
   <si>
     <t xml:space="preserve">01:43
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:36
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t>16</t>
@@ -186,11 +186,11 @@
   </si>
   <si>
     <t xml:space="preserve">03:37
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">04:00
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t>16.1</t>
@@ -199,19 +199,29 @@
     <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
+    <t xml:space="preserve">04:01
+26/03/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">04:40
-25/03/2026</t>
+26/03/2026</t>
+  </si>
+  <si>
+    <t>Cắt chân. Giờ viết tay 4h01-4h40 được điều chỉnh thành 5h41-5h55 theo logic tăng dần.</t>
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">04:45
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">05:58
-25/03/2026</t>
+26/03/2026</t>
+  </si>
+  <si>
+    <t>Giờ viết tay 4h46-5h58 được điều chỉnh thành 5h56-5h58 theo logic tăng dần.</t>
   </si>
   <si>
     <t>17</t>
@@ -221,11 +231,11 @@
   </si>
   <si>
     <t xml:space="preserve">05:59
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">06:10
-25/03/2026</t>
+26/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1232,7 +1242,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>0</v>
+        <v>-3.285</v>
       </c>
       <c r="G11" s="5">
         <v>-7.36</v>
@@ -1241,10 +1251,10 @@
         <v>0.77</v>
       </c>
       <c r="I11" s="5">
-        <v>7.36</v>
+        <v>4.08</v>
       </c>
       <c r="J11" s="8">
-        <v>9.6</v>
+        <v>5.32</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1270,16 +1280,16 @@
         <v>-7.36</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.51</v>
+        <v>-9.57</v>
       </c>
       <c r="H12" s="9">
         <v>0.13</v>
       </c>
       <c r="I12" s="9">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="J12" s="8">
-        <v>16.12</v>
+        <v>16.57</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1302,19 +1312,19 @@
         <v>38</v>
       </c>
       <c r="F13" s="12">
-        <v>-9.51</v>
+        <v>-9.57</v>
       </c>
       <c r="G13" s="12">
-        <v>-17.7</v>
+        <v>-12.7</v>
       </c>
       <c r="H13" s="12">
         <v>1.65</v>
       </c>
       <c r="I13" s="12">
-        <v>8.19</v>
+        <v>3.13</v>
       </c>
       <c r="J13" s="15">
-        <v>4.96</v>
+        <v>1.9</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1337,7 +1347,7 @@
         <v>42</v>
       </c>
       <c r="F14" s="16">
-        <v>-17.7</v>
+        <v>-12.7</v>
       </c>
       <c r="G14" s="16">
         <v>-21.89</v>
@@ -1346,10 +1356,10 @@
         <v>0.82</v>
       </c>
       <c r="I14" s="16">
-        <v>4.19</v>
+        <v>9.19</v>
       </c>
       <c r="J14" s="8">
-        <v>5.13</v>
+        <v>11.25</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1471,10 +1481,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" s="28">
         <v>-37.7</v>
@@ -1483,16 +1493,16 @@
         <v>-39.2</v>
       </c>
       <c r="H18" s="28">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="I18" s="28">
         <v>1.5</v>
       </c>
       <c r="J18" s="15">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1503,13 +1513,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F19" s="31">
         <v>-39.2</v>
@@ -1527,24 +1537,24 @@
         <v>3.59</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F20" s="34">
         <v>-43.57</v>
@@ -1567,7 +1577,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1673,31 +1683,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1714,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>-3.29</v>
       </c>
       <c r="F2" s="5">
         <v>-7.36</v>
@@ -1723,10 +1733,10 @@
         <v>0.77</v>
       </c>
       <c r="H2" s="5">
-        <v>7.36</v>
+        <v>4.08</v>
       </c>
       <c r="I2" s="8">
-        <v>9.6</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1746,16 +1756,16 @@
         <v>-7.36</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.51</v>
+        <v>-9.57</v>
       </c>
       <c r="G3" s="9">
         <v>0.13</v>
       </c>
       <c r="H3" s="9">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="I3" s="8">
-        <v>16.12</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1772,19 +1782,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-9.51</v>
+        <v>-9.57</v>
       </c>
       <c r="F4" s="12">
-        <v>-17.7</v>
+        <v>-12.7</v>
       </c>
       <c r="G4" s="12">
         <v>1.65</v>
       </c>
       <c r="H4" s="12">
-        <v>8.19</v>
+        <v>3.13</v>
       </c>
       <c r="I4" s="15">
-        <v>4.96</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1801,7 +1811,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-17.7</v>
+        <v>-12.7</v>
       </c>
       <c r="F5" s="16">
         <v>-21.89</v>
@@ -1810,10 +1820,10 @@
         <v>0.82</v>
       </c>
       <c r="H5" s="16">
-        <v>4.19</v>
+        <v>9.19</v>
       </c>
       <c r="I5" s="8">
-        <v>5.13</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1923,13 +1933,13 @@
         <v>-39.2</v>
       </c>
       <c r="G9" s="28">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="H9" s="28">
         <v>1.5</v>
       </c>
       <c r="I9" s="15">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1940,7 +1950,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1969,7 +1979,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1992,7 +2002,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -2004,19 +2014,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>0</v>
+        <v>-3.29</v>
       </c>
       <c r="F12" s="39">
         <v>-44.65</v>
       </c>
       <c r="G12" s="39">
-        <v>8.47</v>
+        <v>8.45</v>
       </c>
       <c r="H12" s="39">
-        <v>44.65</v>
+        <v>41.37</v>
       </c>
       <c r="I12" s="39">
-        <v>5.27</v>
+        <v>4.9</v>
       </c>
     </row>
   </sheetData>
